--- a/NBFC-MF/Borrowers/Minarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Minarani_Weekly.xlsx
@@ -2779,31 +2779,33 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="22" t="str">
+      <c r="A4" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>750.92961633393668</v>
+      </c>
+      <c r="F4" s="1">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
+        <v>2249.0703836660632</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>23442.585668039574</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>6557.4143319604264</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>11</v>
@@ -3072,7 +3074,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -3107,7 +3109,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>30000</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -3142,7 +3144,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>25691.656051705635</v>
+        <v>23442.585668039574</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3177,7 +3179,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4308.343948294365</v>
+        <v>6557.4143319604264</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Minarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Minarani_Weekly.xlsx
@@ -2813,31 +2813,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A5" s="19">
+        <v>46289</v>
+      </c>
+      <c r="B5" s="23">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>685.19257093229351</v>
+      </c>
+      <c r="F5" s="21">
+        <f t="shared" si="4"/>
+        <v>2314.8074290677064</v>
+      </c>
+      <c r="G5" s="21">
+        <f t="shared" si="5"/>
+        <v>21127.778238971867</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>8872.2217610281332</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -3074,7 +3076,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -3109,7 +3111,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>27000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -3144,7 +3146,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>23442.585668039574</v>
+        <v>21127.778238971867</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3179,7 +3181,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6557.4143319604264</v>
+        <v>8872.2217610281332</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Minarani_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Minarani_Weekly.xlsx
@@ -2847,31 +2847,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B6" s="22">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>617.53412761908567</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="4"/>
+        <v>2382.4658723809143</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="5"/>
+        <v>18745.312366590952</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>11254.687633409048</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -2879,31 +2881,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46303</v>
+      </c>
+      <c r="B7" s="23">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>547.89812673712129</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" si="4"/>
+        <v>2452.1018732628786</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="5"/>
+        <v>16293.210493328073</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>13706.789506671927</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -3076,7 +3080,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -3111,7 +3115,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>24000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -3146,7 +3150,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>21127.778238971867</v>
+        <v>16293.210493328073</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3181,7 +3185,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>8872.2217610281332</v>
+        <v>13706.789506671927</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
